--- a/presets-source/LSA/Lesson 7/Lesson 7 - Vocab 1.xlsx
+++ b/presets-source/LSA/Lesson 7/Lesson 7 - Vocab 1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8256" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="11100" windowHeight="8232" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -19,78 +19,138 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <x:si>
+    <x:t>v. to learn something</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to become red in the face</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adj. having no mistakes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adj. normal or usual</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notice - noticed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>absorb - absorbed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to pass out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adj. nervous and uncomfortable in front of people</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jimmy always got a perfect score.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to become aware of something</x:t>
+  </x:si>
+  <x:si>
+    <x:t>It was a little hard to notice Jimmy.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to keep or save something in a place</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. information, understanding, or skill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adv. very likely; almost certainly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영어 문장</x:t>
+  </x:si>
   <x:si>
     <x:t>perfect</x:t>
   </x:si>
   <x:si>
+    <x:t>기절하다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한글 뜻</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영어 단어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부끄러워하는</x:t>
+  </x:si>
+  <x:si>
+    <x:t>받아들이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영어 뜻</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장하다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평범한</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완벽한</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아마도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ordinary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>probably</x:t>
+  </x:si>
+  <x:si>
     <x:t>얼굴이 빨개지다</x:t>
   </x:si>
   <x:si>
-    <x:t>평범한</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아마도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ordinary</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notice - noticed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>probably</x:t>
-  </x:si>
-  <x:si>
-    <x:t>absorb - absorbed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영어 뜻</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영어 문장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한글 뜻</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영어 단어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완벽한</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부끄러워하는</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기절하다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>받아들이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장하다</x:t>
+    <x:t>knowledge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알아채다, 인지하다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>blush - blushed</x:t>
   </x:si>
   <x:si>
     <x:t>store - stored</x:t>
   </x:si>
   <x:si>
-    <x:t>blush - blushed</x:t>
-  </x:si>
-  <x:si>
     <x:t>faint - fainted</x:t>
   </x:si>
   <x:si>
-    <x:t>knowledge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알아채다, 인지하다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지식</x:t>
+    <x:t>Maybe that was why Jimmy had such a huge head ㅡ to store all that knowledge.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>His head seemed to absorb everything that was being taught at school.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Everything Jimmy had ever learned was stored somewhere inside his head.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>He was just an ordinary boy who lived with ordinary parents in an ordinary house.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jimmy nearly fainted.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>You probably wouldn't notice him even if he was sitting right next to you.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>He was very, very shy to say anything out loud.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>He blushed all over, and his whole body shook.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -771,19 +831,22 @@
   <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:E11"/>
   <x:sheetFormatPr defaultColWidth="12.62890625" defaultRowHeight="15.75" customHeight="1"/>
+  <x:cols>
+    <x:col min="4" max="4" width="41.171875" bestFit="1" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:5" ht="13.199999999999999">
       <x:c r="B1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="13.199999999999999">
@@ -791,133 +854,173 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:5" ht="13.199999999999999">
       <x:c r="A3" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="13.199999999999999">
       <x:c r="A4" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="13.199999999999999">
       <x:c r="A5" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="1"/>
-      <x:c r="E5" s="1"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:5" ht="13.199999999999999">
       <x:c r="A6" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D6" s="1"/>
-      <x:c r="E6" s="1"/>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:5" ht="13.199999999999999">
       <x:c r="A7" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="1"/>
-      <x:c r="E7" s="1"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:5" ht="13.199999999999999">
       <x:c r="A8" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:5" ht="13.199999999999999">
       <x:c r="A9" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:5" ht="13.199999999999999">
       <x:c r="A10" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
+      <x:c r="E10" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="13.199999999999999">
       <x:c r="A11" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51152777671813965" footer="0.51152777671813965"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>